--- a/importaciones/Prueba carga notificaciones.xlsx
+++ b/importaciones/Prueba carga notificaciones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyectos\Global\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DB2333-B591-4159-B341-592974310C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D83FBA9-B653-4E6F-8363-945E4DE1FE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8F7BE349-DFF4-4E88-B0E4-DD98804FAEB3}"/>
   </bookViews>
@@ -38,37 +38,37 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>"IN-GL-000498"</t>
-  </si>
-  <si>
-    <t>"IN-GL-000497"</t>
-  </si>
-  <si>
-    <t>"IN-IL-005294"</t>
-  </si>
-  <si>
-    <t>"IN-IL-005293"</t>
-  </si>
-  <si>
-    <t>"IN-IL-005292"</t>
-  </si>
-  <si>
-    <t>"IN-IL-005291"</t>
-  </si>
-  <si>
-    <t>"IN-IL-005290"</t>
-  </si>
-  <si>
-    <t>"IN-GL-000496"</t>
-  </si>
-  <si>
-    <t>"IN-BPVC-004013"</t>
-  </si>
-  <si>
     <t>poliza</t>
   </si>
   <si>
     <t>IN-GL-000499</t>
+  </si>
+  <si>
+    <t>IN-GL-000498</t>
+  </si>
+  <si>
+    <t>IN-GL-000497</t>
+  </si>
+  <si>
+    <t>IN-IL-005294</t>
+  </si>
+  <si>
+    <t>IN-IL-005293</t>
+  </si>
+  <si>
+    <t>IN-IL-005292</t>
+  </si>
+  <si>
+    <t>IN-IL-005291</t>
+  </si>
+  <si>
+    <t>IN-IL-005290</t>
+  </si>
+  <si>
+    <t>IN-GL-000496</t>
+  </si>
+  <si>
+    <t>IN-BPVC-004013</t>
   </si>
 </sst>
 </file>
@@ -466,60 +466,63 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0BDFF50-DB23-45B3-B708-011641A430C3}">
   <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
